--- a/artfynd/A 61318-2024 artfynd.xlsx
+++ b/artfynd/A 61318-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121778382</v>
+        <v>121778384</v>
       </c>
       <c r="B2" t="n">
-        <v>94778</v>
+        <v>94885</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2170</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>616221</v>
+        <v>616193</v>
       </c>
       <c r="R2" t="n">
-        <v>6537498</v>
+        <v>6537517</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -1138,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121778384</v>
+        <v>121778382</v>
       </c>
       <c r="B6" t="n">
-        <v>94885</v>
+        <v>94778</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,21 +1154,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>2170</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>616193</v>
+        <v>616221</v>
       </c>
       <c r="R6" t="n">
-        <v>6537517</v>
+        <v>6537498</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 61318-2024 artfynd.xlsx
+++ b/artfynd/A 61318-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121778384</v>
+        <v>121778383</v>
       </c>
       <c r="B2" t="n">
         <v>94885</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>616193</v>
+        <v>616169</v>
       </c>
       <c r="R2" t="n">
-        <v>6537517</v>
+        <v>6537503</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121778387</v>
+        <v>121778384</v>
       </c>
       <c r="B3" t="n">
         <v>94885</v>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616337</v>
+        <v>616193</v>
       </c>
       <c r="R3" t="n">
-        <v>6537603</v>
+        <v>6537517</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121778383</v>
+        <v>121778382</v>
       </c>
       <c r="B4" t="n">
-        <v>94885</v>
+        <v>94778</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>2170</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616169</v>
+        <v>616221</v>
       </c>
       <c r="R4" t="n">
-        <v>6537503</v>
+        <v>6537498</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -986,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121778379</v>
+        <v>121778387</v>
       </c>
       <c r="B5" t="n">
-        <v>78261</v>
+        <v>94885</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,30 +1035,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1066,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>616220</v>
+        <v>616337</v>
       </c>
       <c r="R5" t="n">
-        <v>6537500</v>
+        <v>6537603</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1101,7 +1102,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1112,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121778382</v>
+        <v>121778379</v>
       </c>
       <c r="B6" t="n">
-        <v>94778</v>
+        <v>78261</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,31 +1151,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2170</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>616221</v>
+        <v>616220</v>
       </c>
       <c r="R6" t="n">
-        <v>6537498</v>
+        <v>6537500</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 61318-2024 artfynd.xlsx
+++ b/artfynd/A 61318-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121778383</v>
+        <v>121778387</v>
       </c>
       <c r="B2" t="n">
         <v>94885</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>616169</v>
+        <v>616337</v>
       </c>
       <c r="R2" t="n">
-        <v>6537503</v>
+        <v>6537603</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121778384</v>
+        <v>121778383</v>
       </c>
       <c r="B3" t="n">
         <v>94885</v>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616193</v>
+        <v>616169</v>
       </c>
       <c r="R3" t="n">
-        <v>6537517</v>
+        <v>6537503</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121778382</v>
+        <v>121778384</v>
       </c>
       <c r="B4" t="n">
-        <v>94778</v>
+        <v>94885</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2170</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616221</v>
+        <v>616193</v>
       </c>
       <c r="R4" t="n">
-        <v>6537498</v>
+        <v>6537517</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -986,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121778387</v>
+        <v>121778382</v>
       </c>
       <c r="B5" t="n">
-        <v>94885</v>
+        <v>94778</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,21 +1039,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>2170</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>616337</v>
+        <v>616221</v>
       </c>
       <c r="R5" t="n">
-        <v>6537603</v>
+        <v>6537498</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 61318-2024 artfynd.xlsx
+++ b/artfynd/A 61318-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121778387</v>
+        <v>121778383</v>
       </c>
       <c r="B2" t="n">
         <v>94885</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>616337</v>
+        <v>616169</v>
       </c>
       <c r="R2" t="n">
-        <v>6537603</v>
+        <v>6537503</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121778383</v>
+        <v>121778384</v>
       </c>
       <c r="B3" t="n">
         <v>94885</v>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616169</v>
+        <v>616193</v>
       </c>
       <c r="R3" t="n">
-        <v>6537503</v>
+        <v>6537517</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121778384</v>
+        <v>121778382</v>
       </c>
       <c r="B4" t="n">
-        <v>94885</v>
+        <v>94778</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>2170</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616193</v>
+        <v>616221</v>
       </c>
       <c r="R4" t="n">
-        <v>6537517</v>
+        <v>6537498</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -986,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121778382</v>
+        <v>121778379</v>
       </c>
       <c r="B5" t="n">
-        <v>94778</v>
+        <v>78261</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,31 +1035,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2170</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1067,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>616221</v>
+        <v>616220</v>
       </c>
       <c r="R5" t="n">
-        <v>6537498</v>
+        <v>6537500</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1102,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121778379</v>
+        <v>121778387</v>
       </c>
       <c r="B6" t="n">
-        <v>78261</v>
+        <v>94885</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,30 +1150,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>616220</v>
+        <v>616337</v>
       </c>
       <c r="R6" t="n">
-        <v>6537500</v>
+        <v>6537603</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 61318-2024 artfynd.xlsx
+++ b/artfynd/A 61318-2024 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121778384</v>
+        <v>121778379</v>
       </c>
       <c r="B3" t="n">
-        <v>94885</v>
+        <v>78261</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,31 +803,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -835,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616193</v>
+        <v>616220</v>
       </c>
       <c r="R3" t="n">
-        <v>6537517</v>
+        <v>6537500</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -870,7 +869,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +879,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1023,10 +1022,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121778379</v>
+        <v>121778387</v>
       </c>
       <c r="B5" t="n">
-        <v>78261</v>
+        <v>94885</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,30 +1034,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>616220</v>
+        <v>616337</v>
       </c>
       <c r="R5" t="n">
-        <v>6537500</v>
+        <v>6537603</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,7 +1138,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121778387</v>
+        <v>121778384</v>
       </c>
       <c r="B6" t="n">
         <v>94885</v>
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>616337</v>
+        <v>616193</v>
       </c>
       <c r="R6" t="n">
-        <v>6537603</v>
+        <v>6537517</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 61318-2024 artfynd.xlsx
+++ b/artfynd/A 61318-2024 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121778379</v>
+        <v>121778382</v>
       </c>
       <c r="B3" t="n">
-        <v>78261</v>
+        <v>94778</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,30 +803,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>2170</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616220</v>
+        <v>616221</v>
       </c>
       <c r="R3" t="n">
-        <v>6537500</v>
+        <v>6537498</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -869,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -879,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121778382</v>
+        <v>121778384</v>
       </c>
       <c r="B4" t="n">
-        <v>94778</v>
+        <v>94885</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2170</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -950,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616221</v>
+        <v>616193</v>
       </c>
       <c r="R4" t="n">
-        <v>6537498</v>
+        <v>6537517</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -985,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -995,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1138,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121778384</v>
+        <v>121778379</v>
       </c>
       <c r="B6" t="n">
-        <v>94885</v>
+        <v>78261</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,31 +1151,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>616193</v>
+        <v>616220</v>
       </c>
       <c r="R6" t="n">
-        <v>6537517</v>
+        <v>6537500</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 61318-2024 artfynd.xlsx
+++ b/artfynd/A 61318-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121778383</v>
+        <v>121778382</v>
       </c>
       <c r="B2" t="n">
-        <v>94885</v>
+        <v>94796</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>2170</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>616169</v>
+        <v>616221</v>
       </c>
       <c r="R2" t="n">
-        <v>6537503</v>
+        <v>6537498</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121778382</v>
+        <v>121778383</v>
       </c>
       <c r="B3" t="n">
-        <v>94778</v>
+        <v>94903</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2170</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616221</v>
+        <v>616169</v>
       </c>
       <c r="R3" t="n">
-        <v>6537498</v>
+        <v>6537503</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,7 +910,7 @@
         <v>121778384</v>
       </c>
       <c r="B4" t="n">
-        <v>94885</v>
+        <v>94903</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121778387</v>
+        <v>121778379</v>
       </c>
       <c r="B5" t="n">
-        <v>94885</v>
+        <v>78274</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,31 +1035,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1067,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>616337</v>
+        <v>616220</v>
       </c>
       <c r="R5" t="n">
-        <v>6537603</v>
+        <v>6537500</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1102,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121778379</v>
+        <v>121778387</v>
       </c>
       <c r="B6" t="n">
-        <v>78261</v>
+        <v>94903</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,30 +1150,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>616220</v>
+        <v>616337</v>
       </c>
       <c r="R6" t="n">
-        <v>6537500</v>
+        <v>6537603</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD6" t="b">
